--- a/docs/03-dane/fixtures/anonymized/xtb/xtb-syntetyczny-stary-szablon-PLN.xlsx
+++ b/docs/03-dane/fixtures/anonymized/xtb/xtb-syntetyczny-stary-szablon-PLN.xlsx
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45901.66856481481</v>
+        <v>45902.66856481481</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45901.66856481481</v>
+        <v>45902.66856481481</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SEC FEE 2025-09-01</t>
+          <t>SEC FEE 2025-09-02</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1118,7 +1118,7 @@
         <v>240</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45901.66856481481</v>
+        <v>45902.66856481481</v>
       </c>
       <c r="I14" t="n">
         <v>230</v>
